--- a/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
@@ -2165,40 +2165,40 @@
       <c r="P19" s="45" t="n"/>
       <c r="Q19" s="1" t="n"/>
     </row>
-    <row r="20" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A20" s="15" t="n">
+    <row r="20" ht="53.05" customFormat="1" customHeight="1" s="98">
+      <c r="A20" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="149" t="n">
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+      <c r="F20" s="38" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="133" t="n">
         <v>46293</v>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="I20" s="39" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr">
+      <c r="J20" s="37" t="inlineStr">
         <is>
           <t>アイカ モルタルアートのサンプル作成のため、カタログより色を選定してほしい</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="K20" s="36" t="inlineStr">
         <is>
           <t>NS
 SJ</t>
         </is>
       </c>
-      <c r="L20" s="33" t="inlineStr">
+      <c r="L20" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2213,56 +2213,57 @@
           <r>
             <rPr>
               <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-              <charset val="128"/>
-              <family val="3"/>
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
-            <t>・10/2 第3回分科会　A4サンプルにてCM02・CM15・CM30で確認</t>
+            <t>・10/2 第3回分科会　A4サンプルにてCM02・CM15・CM30で確認
+・10/21　理事長プレゼンにて決定</t>
           </r>
         </is>
       </c>
-      <c r="M20" s="153" t="n"/>
-      <c r="N20" s="151" t="n">
+      <c r="M20" s="134" t="n"/>
+      <c r="N20" s="135" t="n">
         <v>46316</v>
       </c>
-      <c r="O20" s="152" t="n"/>
-      <c r="P20" s="20" t="n"/>
+      <c r="O20" s="136" t="n">
+        <v>46316</v>
+      </c>
+      <c r="P20" s="45" t="n"/>
       <c r="Q20" s="1" t="n"/>
     </row>
-    <row r="21" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A21" s="15" t="n">
+    <row r="21" ht="53.05" customFormat="1" customHeight="1" s="98">
+      <c r="A21" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="149" t="n">
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="38" t="n"/>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="38" t="n"/>
+      <c r="H21" s="133" t="n">
         <v>46293</v>
       </c>
-      <c r="I21" s="24" t="inlineStr">
+      <c r="I21" s="39" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J21" s="18" t="inlineStr">
+      <c r="J21" s="37" t="inlineStr">
         <is>
           <t>吸音ルーバーの固定方法確認（ASタイプのZ金物20mmが標準品）、色サンプル作成用の日塗工品番指示（既製品は白）</t>
         </is>
       </c>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="K21" s="36" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L21" s="33" t="inlineStr">
+      <c r="L21" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2277,21 +2278,22 @@
           <r>
             <rPr>
               <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-              <charset val="128"/>
-              <family val="3"/>
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
-            <t>・10/2 第3回分科会　同形状で間に合うのは白のみ。色は他のサンプルで決める</t>
+            <t>・10/2 第3回分科会　同形状で間に合うのは白のみ。色は他のサンプルで決める
+・10/21　理事長プレゼンにて決定</t>
           </r>
         </is>
       </c>
-      <c r="M21" s="153" t="n"/>
-      <c r="N21" s="151" t="n">
+      <c r="M21" s="134" t="n"/>
+      <c r="N21" s="135" t="n">
         <v>46316</v>
       </c>
-      <c r="O21" s="152" t="n"/>
-      <c r="P21" s="20" t="n"/>
+      <c r="O21" s="136" t="n">
+        <v>46316</v>
+      </c>
+      <c r="P21" s="45" t="n"/>
       <c r="Q21" s="1" t="n"/>
     </row>
     <row r="22" ht="88.05" customFormat="1" customHeight="1" s="98">

--- a/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
@@ -2441,56 +2441,73 @@
       <c r="P23" s="20" t="n"/>
       <c r="Q23" s="1" t="n"/>
     </row>
-    <row r="24" ht="49.05" customFormat="1" customHeight="1" s="98">
-      <c r="A24" s="15" t="n">
+    <row r="24" ht="62.05" customFormat="1" customHeight="1" s="98">
+      <c r="A24" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="149" t="n">
+      <c r="D24" s="38" t="n"/>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="38" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="133" t="n">
         <v>46293</v>
       </c>
-      <c r="I24" s="24" t="inlineStr">
+      <c r="I24" s="39" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J24" s="37" t="inlineStr">
         <is>
           <t>ハンガードア（CH3150）
 ①床側固定（タイル固定か躯体アンカーか、金物仕様）
 ②上部下地（LGS可否検討中。鉄骨下地の場合は追加）</t>
         </is>
       </c>
-      <c r="K24" s="17" t="inlineStr">
+      <c r="K24" s="36" t="inlineStr">
         <is>
           <t>NS
 SC</t>
         </is>
       </c>
-      <c r="L24" s="33" t="inlineStr">
-        <is>
-          <t>・9/28 第1回分科会　SCにて検討中</t>
-        </is>
-      </c>
-      <c r="M24" s="153" t="n"/>
-      <c r="N24" s="151" t="n">
+      <c r="L24" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">・9/28 第1回分科会　SCにて検討中
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <color rgb="FFFF0000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>・10/14 第4回分科会　①床側はアンカー固定、②上部は鉄骨下地とすることで決定</t>
+          </r>
+        </is>
+      </c>
+      <c r="M24" s="134" t="n"/>
+      <c r="N24" s="135" t="n">
         <v>46325</v>
       </c>
-      <c r="O24" s="152" t="n"/>
-      <c r="P24" s="20" t="n"/>
+      <c r="O24" s="136" t="n">
+        <v>46309</v>
+      </c>
+      <c r="P24" s="45" t="n"/>
       <c r="Q24" s="1" t="n"/>
     </row>
     <row r="25" ht="62.05" customFormat="1" customHeight="1" s="98">

--- a/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
@@ -2571,45 +2571,45 @@
       <c r="P25" s="20" t="n"/>
       <c r="Q25" s="1" t="n"/>
     </row>
-    <row r="26" ht="62.1" customFormat="1" customHeight="1" s="98">
-      <c r="A26" s="15" t="n">
+    <row r="26" ht="75.09999999999999" customFormat="1" customHeight="1" s="98">
+      <c r="A26" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="149" t="n">
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="38" t="n"/>
+      <c r="G26" s="38" t="n"/>
+      <c r="H26" s="133" t="n">
         <v>46293</v>
       </c>
-      <c r="I26" s="24" t="inlineStr">
+      <c r="I26" s="39" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J26" s="18" t="inlineStr">
+      <c r="J26" s="37" t="inlineStr">
         <is>
           <t>鋼製床（東洋工業：JIS規格品ではない）
 ①採用可否・必要性能・確認資料、設計承認の状況
 ②点検口の要否・設置数（H800床下は人が入れない）</t>
         </is>
       </c>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="K26" s="36" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="L26" s="33" t="inlineStr">
+      <c r="L26" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2624,21 +2624,22 @@
           <r>
             <rPr>
               <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-              <charset val="128"/>
-              <family val="3"/>
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
-            <t>・10/9　点検口は保留のまま</t>
+            <t>・10/9　点検口は保留のまま
+・10/14 第4回分科会　東側デッキの立上り側面に点検口（600角）を設置することで決定</t>
           </r>
         </is>
       </c>
-      <c r="M26" s="153" t="n"/>
-      <c r="N26" s="151" t="n">
+      <c r="M26" s="134" t="n"/>
+      <c r="N26" s="135" t="n">
         <v>46325</v>
       </c>
-      <c r="O26" s="152" t="n"/>
-      <c r="P26" s="20" t="n"/>
+      <c r="O26" s="136" t="n">
+        <v>46309</v>
+      </c>
+      <c r="P26" s="45" t="n"/>
       <c r="Q26" s="1" t="n"/>
     </row>
     <row r="27" ht="49.05" customFormat="1" customHeight="1" s="98">

--- a/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
@@ -2774,58 +2774,75 @@
       <c r="P28" s="45" t="n"/>
       <c r="Q28" s="1" t="n"/>
     </row>
-    <row r="29" ht="75" customFormat="1" customHeight="1" s="98">
-      <c r="A29" s="46" t="n">
+    <row r="29" ht="88" customFormat="1" customHeight="1" s="98">
+      <c r="A29" s="51" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="47" t="inlineStr">
+      <c r="B29" s="52" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C29" s="47" t="n"/>
-      <c r="D29" s="47" t="n"/>
-      <c r="E29" s="47" t="inlineStr">
+      <c r="C29" s="52" t="n"/>
+      <c r="D29" s="52" t="n"/>
+      <c r="E29" s="52" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="F29" s="47" t="n"/>
-      <c r="G29" s="47" t="n"/>
-      <c r="H29" s="151" t="n">
+      <c r="F29" s="52" t="n"/>
+      <c r="G29" s="52" t="n"/>
+      <c r="H29" s="135" t="n">
         <v>46297</v>
       </c>
-      <c r="I29" s="48" t="inlineStr">
+      <c r="I29" s="53" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J29" s="49" t="inlineStr">
+      <c r="J29" s="54" t="inlineStr">
         <is>
           <t>タイル割（基本方針で作図したタイル割、階段・スロープの割付）の確認</t>
         </is>
       </c>
-      <c r="K29" s="87" t="inlineStr">
+      <c r="K29" s="88" t="inlineStr">
         <is>
           <t>NS
 SC</t>
         </is>
       </c>
-      <c r="L29" s="50" t="inlineStr">
-        <is>
-          <t>・10/2 第3回分科会　階段踏面はタイル割により288mmとする→OK
+      <c r="L29" s="55" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">・10/2 第3回分科会　階段踏面はタイル割により288mmとする→OK
 ・段鼻は80（蹴上）×40（踏面）、蹴上は縦張り
 ・中央階段は段鼻タイルの終わりから真物になるよう割りはじめる
 ・スロープ最下部の曲がり位置をしっかり出すため、既存タイルを撤去し下地モルタルで調整
-・タイル部の空調は吸込みをカウンター下、吹出しをSSD際とする希望あり</t>
-        </is>
-      </c>
-      <c r="M29" s="154" t="n"/>
-      <c r="N29" s="151" t="n">
+・タイル部の空調は吸込みをカウンター下、吹出しをSSD際とする希望あり
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <color rgb="FFFF0000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>・10/14　決定</t>
+          </r>
+        </is>
+      </c>
+      <c r="M29" s="158" t="n"/>
+      <c r="N29" s="135" t="n">
         <v>46325</v>
       </c>
-      <c r="O29" s="155" t="n"/>
-      <c r="P29" s="43" t="n"/>
+      <c r="O29" s="136" t="n">
+        <v>46309</v>
+      </c>
+      <c r="P29" s="56" t="n"/>
       <c r="Q29" s="1" t="n"/>
     </row>
     <row r="30" ht="53.1" customFormat="1" customHeight="1" s="98">

--- a/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
@@ -2892,51 +2892,68 @@
       <c r="P30" s="43" t="n"/>
       <c r="Q30" s="1" t="n"/>
     </row>
-    <row r="31" ht="53.1" customFormat="1" customHeight="1" s="98">
-      <c r="A31" s="46" t="n">
+    <row r="31" ht="66.09999999999999" customFormat="1" customHeight="1" s="98">
+      <c r="A31" s="51" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="47" t="inlineStr">
+      <c r="B31" s="52" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C31" s="47" t="n"/>
-      <c r="D31" s="47" t="n"/>
-      <c r="E31" s="47" t="n"/>
-      <c r="F31" s="47" t="n"/>
-      <c r="G31" s="47" t="n"/>
-      <c r="H31" s="151" t="n">
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+      <c r="E31" s="52" t="n"/>
+      <c r="F31" s="52" t="n"/>
+      <c r="G31" s="52" t="n"/>
+      <c r="H31" s="135" t="n">
         <v>46297</v>
       </c>
-      <c r="I31" s="48" t="inlineStr">
+      <c r="I31" s="53" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J31" s="49" t="inlineStr">
+      <c r="J31" s="54" t="inlineStr">
         <is>
           <t>ロールスクリーンの選定</t>
         </is>
       </c>
-      <c r="K31" s="87" t="inlineStr">
+      <c r="K31" s="88" t="inlineStr">
         <is>
           <t>NS
 SJ</t>
         </is>
       </c>
-      <c r="L31" s="50" t="inlineStr">
-        <is>
-          <t>・10/2 第3回分科会　カタログで選択したものをSCにてA4サイズのサンプル手配。TOSOも見積する
-・10/9　NSよりサンプルの指示あり</t>
-        </is>
-      </c>
-      <c r="M31" s="154" t="n"/>
-      <c r="N31" s="151" t="n">
+      <c r="L31" s="55" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">・10/2 第3回分科会　カタログで選択したものをSCにてA4サイズのサンプル手配。TOSOも見積する
+・10/9　NSよりサンプルの指示あり
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
+              <color rgb="FFFF0000"/>
+              <sz val="9"/>
+            </rPr>
+            <t>・10/14 第4回分科会にて決定</t>
+          </r>
+        </is>
+      </c>
+      <c r="M31" s="158" t="n"/>
+      <c r="N31" s="135" t="n">
         <v>46316</v>
       </c>
-      <c r="O31" s="155" t="n"/>
-      <c r="P31" s="43" t="n"/>
+      <c r="O31" s="136" t="n">
+        <v>46309</v>
+      </c>
+      <c r="P31" s="56" t="n"/>
       <c r="Q31" s="1" t="n"/>
     </row>
     <row r="32" ht="40.05" customFormat="1" customHeight="1" s="98">

--- a/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
@@ -3403,49 +3403,52 @@
       <c r="P40" s="123" t="n"/>
       <c r="Q40" s="1" t="n"/>
     </row>
-    <row r="41" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A41" s="46" t="n">
+    <row r="41" ht="53.05" customFormat="1" customHeight="1" s="98">
+      <c r="A41" s="51" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="47" t="inlineStr">
+      <c r="B41" s="52" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C41" s="47" t="n"/>
-      <c r="D41" s="47" t="n"/>
-      <c r="E41" s="47" t="n"/>
-      <c r="F41" s="47" t="n"/>
-      <c r="G41" s="47" t="n"/>
-      <c r="H41" s="151" t="n">
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+      <c r="E41" s="52" t="n"/>
+      <c r="F41" s="52" t="n"/>
+      <c r="G41" s="52" t="n"/>
+      <c r="H41" s="135" t="n">
         <v>46309</v>
       </c>
-      <c r="I41" s="48" t="inlineStr">
+      <c r="I41" s="53" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J41" s="49" t="inlineStr">
+      <c r="J41" s="54" t="inlineStr">
         <is>
           <t>ガラリ部のルーバー貼付けは無しとしたい。また天井ルーバーが干渉する</t>
         </is>
       </c>
-      <c r="K41" s="87" t="inlineStr">
+      <c r="K41" s="88" t="inlineStr">
         <is>
           <t>NS
 SC</t>
         </is>
       </c>
-      <c r="L41" s="50" t="inlineStr">
+      <c r="L41" s="55" t="inlineStr">
         <is>
           <t>・10/14 第4回分科会　ガラリの上のルーバーは無しとする
-・天井ルーバーの干渉は範囲を検討。裏から点検できない可能性も含めて現地確認・検討する</t>
-        </is>
-      </c>
-      <c r="M41" s="154" t="n"/>
-      <c r="N41" s="151" t="n"/>
-      <c r="O41" s="155" t="n"/>
-      <c r="P41" s="43" t="n"/>
+・天井ルーバーの干渉は範囲を検討。裏から点検できない可能性も含めて現地確認・検討する
+・10/19 分科会　ガラリ面および天井面の吸音ルーバーは中止で決定</t>
+        </is>
+      </c>
+      <c r="M41" s="158" t="n"/>
+      <c r="N41" s="135" t="n"/>
+      <c r="O41" s="136" t="n">
+        <v>46314</v>
+      </c>
+      <c r="P41" s="56" t="n"/>
       <c r="Q41" s="2" t="n"/>
     </row>
     <row r="42" ht="49" customFormat="1" customHeight="1" s="98">

--- a/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
+++ b/椙山改修/261030_課題リスト（1014_分科会後）.xlsx
@@ -1765,7 +1765,7 @@
       <c r="P13" s="45" t="n"/>
       <c r="Q13" s="1" t="n"/>
     </row>
-    <row r="14" ht="101.1" customFormat="1" customHeight="1" s="98">
+    <row r="14" ht="114.1" customFormat="1" customHeight="1" s="98">
       <c r="A14" s="34" t="n">
         <v>9</v>
       </c>
@@ -1815,14 +1815,13 @@
           <r>
             <rPr>
               <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-              <charset val="128"/>
-              <family val="3"/>
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
             <t>・10/2 第3回分科会　腰壁コーナー納まりのサンプルは10/9中に完成予定
 ・同　コーナーの方針はOK。現場ではコーナー目地をなるべく小さく、入隅は目地が少し大きくなってもよい。コーナーは取り合うタイルの色を合わせる→SCにて図面反映
-・10/9　NSにてモックアップを確認、OK</t>
+・10/9　NSにてモックアップを確認、OK
+・10/23 第6回分科会（理事長プレゼン最終確認）　織部製陶に決定、腰壁の天端と側面は色を合わせる。アイスランドは1：1のMIXに決定。床目地色は濃灰（要確認）</t>
           </r>
         </is>
       </c>
@@ -2165,7 +2164,7 @@
       <c r="P19" s="45" t="n"/>
       <c r="Q19" s="1" t="n"/>
     </row>
-    <row r="20" ht="53.05" customFormat="1" customHeight="1" s="98">
+    <row r="20" ht="66.05" customFormat="1" customHeight="1" s="98">
       <c r="A20" s="34" t="n">
         <v>15</v>
       </c>
@@ -2217,7 +2216,8 @@
               <sz val="9"/>
             </rPr>
             <t>・10/2 第3回分科会　A4サンプルにてCM02・CM15・CM30で確認
-・10/21　理事長プレゼンにて決定</t>
+・10/21　理事長プレゼンにて決定
+・10/23 第6回分科会（理事長プレゼン最終確認）　CM15・CM30の色分け範囲を確認</t>
           </r>
         </is>
       </c>
@@ -2231,7 +2231,7 @@
       <c r="P20" s="45" t="n"/>
       <c r="Q20" s="1" t="n"/>
     </row>
-    <row r="21" ht="53.05" customFormat="1" customHeight="1" s="98">
+    <row r="21" ht="66.05" customFormat="1" customHeight="1" s="98">
       <c r="A21" s="34" t="n">
         <v>16</v>
       </c>
@@ -2282,7 +2282,8 @@
               <sz val="9"/>
             </rPr>
             <t>・10/2 第3回分科会　同形状で間に合うのは白のみ。色は他のサンプルで決める
-・10/21　理事長プレゼンにて決定</t>
+・10/21　理事長プレゼンにて決定
+・10/23 第6回分科会（理事長プレゼン最終確認）　吸音ルーバーの色はN85</t>
           </r>
         </is>
       </c>
@@ -2296,7 +2297,7 @@
       <c r="P21" s="45" t="n"/>
       <c r="Q21" s="1" t="n"/>
     </row>
-    <row r="22" ht="88.05" customFormat="1" customHeight="1" s="98">
+    <row r="22" ht="101.05" customFormat="1" customHeight="1" s="98">
       <c r="A22" s="34" t="n">
         <v>17</v>
       </c>
@@ -2351,13 +2352,12 @@
           <r>
             <rPr>
               <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-              <charset val="128"/>
-              <family val="3"/>
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
             <t>・10/2 第3回分科会　③ルーバー裏の塗装はダウンライト等の器具と共色とし、照明器具仕様書に合わせN95で進める
-・10/2　完了</t>
+・10/2　完了
+・10/23 第6回分科会（理事長プレゼン最終確認）　吸音ルーバー裏の色はN3（10/2時点のN95から変更か要確認）</t>
           </r>
         </is>
       </c>
@@ -2642,7 +2642,7 @@
       <c r="P26" s="45" t="n"/>
       <c r="Q26" s="1" t="n"/>
     </row>
-    <row r="27" ht="49.05" customFormat="1" customHeight="1" s="98">
+    <row r="27" ht="62.05" customFormat="1" customHeight="1" s="98">
       <c r="A27" s="15" t="n">
         <v>22</v>
       </c>
@@ -2690,12 +2690,11 @@
           <r>
             <rPr>
               <rFont val="HG丸ｺﾞｼｯｸM-PRO"/>
-              <charset val="128"/>
-              <family val="3"/>
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
-            <t>・10/2 第3回分科会　無垢と集成材の2パターンでサンプル確認。SCはウレタンクリア塗装まで施したサンプルを用意する</t>
+            <t>・10/2 第3回分科会　無垢と集成材の2パターンでサンプル確認。SCはウレタンクリア塗装まで施したサンプルを用意する
+・10/23 第6回分科会（理事長プレゼン最終確認）　木パネルは集成材。製作図でランダムに指示する</t>
           </r>
         </is>
       </c>
@@ -2845,54 +2844,57 @@
       <c r="P29" s="56" t="n"/>
       <c r="Q29" s="1" t="n"/>
     </row>
-    <row r="30" ht="53.1" customFormat="1" customHeight="1" s="98">
-      <c r="A30" s="46" t="n">
+    <row r="30" ht="66.09999999999999" customFormat="1" customHeight="1" s="98">
+      <c r="A30" s="51" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="47" t="inlineStr">
+      <c r="B30" s="52" t="inlineStr">
         <is>
           <t>〇</t>
         </is>
       </c>
-      <c r="C30" s="47" t="n"/>
-      <c r="D30" s="47" t="n"/>
-      <c r="E30" s="47" t="n"/>
-      <c r="F30" s="47" t="n"/>
-      <c r="G30" s="47" t="n"/>
-      <c r="H30" s="151" t="n">
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+      <c r="E30" s="52" t="n"/>
+      <c r="F30" s="52" t="n"/>
+      <c r="G30" s="52" t="n"/>
+      <c r="H30" s="135" t="n">
         <v>46297</v>
       </c>
-      <c r="I30" s="48" t="inlineStr">
+      <c r="I30" s="53" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="J30" s="49" t="inlineStr">
+      <c r="J30" s="54" t="inlineStr">
         <is>
           <t>アルミルーバーの色をサンプルにて確認</t>
         </is>
       </c>
-      <c r="K30" s="87" t="inlineStr">
+      <c r="K30" s="88" t="inlineStr">
         <is>
           <t>NS
 SJ</t>
         </is>
       </c>
-      <c r="L30" s="50" t="inlineStr">
+      <c r="L30" s="55" t="inlineStr">
         <is>
           <t>・10/2 第3回分科会　シルバーで決定。SCにてシルクカラーのコストを確認する
-・10/9　NSよりマット色の比較検討依頼あり</t>
-        </is>
-      </c>
-      <c r="M30" s="154" t="n"/>
-      <c r="N30" s="151" t="n">
+・10/9　NSよりマット色の比較検討依頼あり
+・10/23 第6回分科会（理事長プレゼン最終確認）　型番を変更し、色はシルクシルバーに決定</t>
+        </is>
+      </c>
+      <c r="M30" s="158" t="n"/>
+      <c r="N30" s="135" t="n">
         <v>46316</v>
       </c>
-      <c r="O30" s="155" t="n"/>
-      <c r="P30" s="43" t="n"/>
+      <c r="O30" s="136" t="n">
+        <v>46316</v>
+      </c>
+      <c r="P30" s="56" t="n"/>
       <c r="Q30" s="1" t="n"/>
     </row>
-    <row r="31" ht="66.09999999999999" customFormat="1" customHeight="1" s="98">
+    <row r="31" ht="79.09999999999999" customFormat="1" customHeight="1" s="98">
       <c r="A31" s="51" t="n">
         <v>26</v>
       </c>
@@ -2942,7 +2944,8 @@
               <color rgb="FFFF0000"/>
               <sz val="9"/>
             </rPr>
-            <t>・10/14 第4回分科会にて決定</t>
+            <t>・10/14 第4回分科会にて決定
+・10/23 第6回分科会（理事長プレゼン最終確認）　デイズ遮熱、色はアイスグレー、スパン2分割</t>
           </r>
         </is>
       </c>
@@ -2956,7 +2959,7 @@
       <c r="P31" s="56" t="n"/>
       <c r="Q31" s="1" t="n"/>
     </row>
-    <row r="32" ht="40.05" customFormat="1" customHeight="1" s="98">
+    <row r="32" ht="53.05" customFormat="1" customHeight="1" s="98">
       <c r="A32" s="115" t="n">
         <v>27</v>
       </c>
@@ -2991,7 +2994,8 @@
       </c>
       <c r="L32" s="121" t="inlineStr">
         <is>
-          <t>・10/2 第3回分科会　カタログで選択したものをSCにて手配</t>
+          <t>・10/2 第3回分科会　カタログで選択したものをSCにて手配
+・10/23 第6回分科会（理事長プレゼン最終確認）　支柱はステンカラー、幕はライトグレー（パラソルの色次第）</t>
         </is>
       </c>
       <c r="M32" s="157" t="n"/>
@@ -3496,23 +3500,55 @@
       <c r="P42" s="43" t="n"/>
       <c r="Q42" s="1" t="n"/>
     </row>
-    <row r="43" ht="40.05" customFormat="1" customHeight="1" s="98">
-      <c r="A43" s="15" t="n"/>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-      <c r="G43" s="16" t="n"/>
-      <c r="H43" s="149" t="n"/>
-      <c r="I43" s="24" t="n"/>
-      <c r="J43" s="18" t="n"/>
-      <c r="K43" s="17" t="n"/>
-      <c r="L43" s="25" t="n"/>
-      <c r="M43" s="153" t="n"/>
-      <c r="N43" s="149" t="n"/>
-      <c r="O43" s="19" t="n"/>
-      <c r="P43" s="20" t="n"/>
+    <row r="43" ht="62" customFormat="1" customHeight="1" s="98">
+      <c r="A43" s="46" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="47" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="C43" s="47" t="n"/>
+      <c r="D43" s="47" t="n"/>
+      <c r="E43" s="47" t="n"/>
+      <c r="F43" s="47" t="n"/>
+      <c r="G43" s="47" t="n"/>
+      <c r="H43" s="151" t="n">
+        <v>46318</v>
+      </c>
+      <c r="I43" s="48" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="J43" s="49" t="inlineStr">
+        <is>
+          <t>理事長プレゼン（10/21）後の未決事項
+・ルーバー裏のガラスフィルムの色
+・ストリングカーテンの色
+・メタカラーの色</t>
+        </is>
+      </c>
+      <c r="K43" s="87" t="inlineStr">
+        <is>
+          <t>NS
+SJ
+SC</t>
+        </is>
+      </c>
+      <c r="L43" s="50" t="inlineStr">
+        <is>
+          <t>・10/23 第6回分科会（理事長プレゼン最終確認）
+・ルーバー裏ガラスフィルムはミルキーホワイト（要確認）
+・ストリングカーテンは別品番にシルバーあり→サンプルを取る
+・メタカラーの色は未定</t>
+        </is>
+      </c>
+      <c r="M43" s="154" t="n"/>
+      <c r="N43" s="151" t="n"/>
+      <c r="O43" s="155" t="n"/>
+      <c r="P43" s="43" t="n"/>
     </row>
     <row r="44" ht="40.05" customFormat="1" customHeight="1" s="98">
       <c r="A44" s="15" t="n"/>
